--- a/turni.xlsx
+++ b/turni.xlsx
@@ -2012,7 +2012,7 @@
         <v>25</v>
       </c>
       <c r="J14" t="s" s="4">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K14" t="s" s="4">
         <v>36</v>
@@ -2192,7 +2192,7 @@
         <v>25</v>
       </c>
       <c r="J18" t="s" s="4">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K18" t="s" s="4">
         <v>36</v>
@@ -2366,7 +2366,7 @@
         <v>25</v>
       </c>
       <c r="J22" t="s" s="4">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K22" t="s" s="4">
         <v>36</v>
@@ -2596,7 +2596,7 @@
         <v>25</v>
       </c>
       <c r="J27" t="s" s="4">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="K27" t="s" s="4">
         <v>36</v>
